--- a/per-stock/AMD/financials.xlsx
+++ b/per-stock/AMD/financials.xlsx
@@ -1,19 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Income stmt (annual)" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Income stmt (quarterly)" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Balance sheet (annual)" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash flow (annual)" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash flow (quarterly)" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data flags" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="FY Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Income stmt (annual)" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Income stmt (quarterly)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Balance sheet (annual)" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Balance sheet (quarterly)" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Cash flow (annual)" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Cash flow (quarterly)" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Data flags" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,7 +24,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+    <numFmt numFmtId="165" formatCode="0.00&quot;x&quot;"/>
+    <numFmt numFmtId="166" formatCode="#,##0.0"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -61,11 +67,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -531,7 +540,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>691537707008</v>
+        <v>876235849728</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -546,7 +555,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>683061739520</v>
+        <v>867759882240</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -561,7 +570,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>140.89702</v>
+        <v>178.52824</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -576,7 +585,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>32.73839</v>
+        <v>41.00965</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -591,7 +600,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>18.463654</v>
+        <v>23.394987</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -711,11 +720,11 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>7173374976</v>
+        <v>8574000000</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>yfinance info.freeCashflow</t>
+          <t>statement: TTM OCF - |capex| (yfinance quarterly_cashflow)</t>
         </is>
       </c>
     </row>
@@ -741,7 +750,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>424.1</v>
+        <v>537.37</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -785,6 +794,465 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="52" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Fiscal-year summary (GAAP, $ except where noted)</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>FY-3</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>FY-2</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>FY-1</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>TTM</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Source / formula</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Fiscal period end</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2023-12-31</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2024-12-31</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>TTM → 2026-03-31</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>annual statement headers; TTM = Σ last 4 quarters</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B3" s="3">
+        <f>'Income stmt (annual)'!D54</f>
+        <v/>
+      </c>
+      <c r="C3" s="3">
+        <f>'Income stmt (annual)'!C54</f>
+        <v/>
+      </c>
+      <c r="D3" s="3">
+        <f>'Income stmt (annual)'!B54</f>
+        <v/>
+      </c>
+      <c r="E3" s="3">
+        <f>SUM('Income stmt (quarterly)'!B44:E44)</f>
+        <v/>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Total Revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Gross profit</t>
+        </is>
+      </c>
+      <c r="B4" s="3">
+        <f>'Income stmt (annual)'!D52</f>
+        <v/>
+      </c>
+      <c r="C4" s="3">
+        <f>'Income stmt (annual)'!C52</f>
+        <v/>
+      </c>
+      <c r="D4" s="3">
+        <f>'Income stmt (annual)'!B52</f>
+        <v/>
+      </c>
+      <c r="E4" s="3">
+        <f>SUM('Income stmt (quarterly)'!B42:E42)</f>
+        <v/>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Gross Profit (GAAP)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Gross margin %</t>
+        </is>
+      </c>
+      <c r="B5" s="4">
+        <f>IFERROR(B4/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C5" s="4">
+        <f>IFERROR(C4/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D5" s="4">
+        <f>IFERROR(D4/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E5" s="4">
+        <f>IFERROR(E4/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>GAAP = gross profit / revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Operating income</t>
+        </is>
+      </c>
+      <c r="B6" s="3">
+        <f>'Income stmt (annual)'!D43</f>
+        <v/>
+      </c>
+      <c r="C6" s="3">
+        <f>'Income stmt (annual)'!C43</f>
+        <v/>
+      </c>
+      <c r="D6" s="3">
+        <f>'Income stmt (annual)'!B43</f>
+        <v/>
+      </c>
+      <c r="E6" s="3">
+        <f>SUM('Income stmt (quarterly)'!B33:E33)</f>
+        <v/>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Operating Income</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Operating margin %</t>
+        </is>
+      </c>
+      <c r="B7" s="4">
+        <f>IFERROR(B6/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C7" s="4">
+        <f>IFERROR(C6/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D7" s="4">
+        <f>IFERROR(D6/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E7" s="4">
+        <f>IFERROR(E6/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F7">
+        <f> operating income / revenue</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+      <c r="B8" s="3">
+        <f>'Income stmt (annual)'!D10</f>
+        <v/>
+      </c>
+      <c r="C8" s="3">
+        <f>'Income stmt (annual)'!C10</f>
+        <v/>
+      </c>
+      <c r="D8" s="3">
+        <f>'Income stmt (annual)'!B10</f>
+        <v/>
+      </c>
+      <c r="E8" s="3">
+        <f>SUM('Income stmt (quarterly)'!B8:E8)</f>
+        <v/>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Free cash flow</t>
+        </is>
+      </c>
+      <c r="B9" s="3">
+        <f>'Cash flow (annual)'!D2</f>
+        <v/>
+      </c>
+      <c r="C9" s="3">
+        <f>'Cash flow (annual)'!C2</f>
+        <v/>
+      </c>
+      <c r="D9" s="3">
+        <f>'Cash flow (annual)'!B2</f>
+        <v/>
+      </c>
+      <c r="E9" s="3">
+        <f>SUM('Cash flow (quarterly)'!B2:E2)</f>
+        <v/>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>FCF = OCF − capex</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>FCF margin %</t>
+        </is>
+      </c>
+      <c r="B10" s="4">
+        <f>IFERROR(B9/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C10" s="4">
+        <f>IFERROR(C9/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D10" s="4">
+        <f>IFERROR(D9/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E10" s="4">
+        <f>IFERROR(E9/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F10">
+        <f> FCF / revenue</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Capex</t>
+        </is>
+      </c>
+      <c r="B11" s="3">
+        <f>-'Cash flow (annual)'!D6</f>
+        <v/>
+      </c>
+      <c r="C11" s="3">
+        <f>-'Cash flow (annual)'!C6</f>
+        <v/>
+      </c>
+      <c r="D11" s="3">
+        <f>-'Cash flow (annual)'!B6</f>
+        <v/>
+      </c>
+      <c r="E11" s="3">
+        <f>-SUM('Cash flow (quarterly)'!B6:E6)</f>
+        <v/>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Capex (shown positive)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Capex / revenue %</t>
+        </is>
+      </c>
+      <c r="B12" s="4">
+        <f>IFERROR(B11/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C12" s="4">
+        <f>IFERROR(C11/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D12" s="4">
+        <f>IFERROR(D11/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E12" s="4">
+        <f>IFERROR(E11/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F12">
+        <f> capex / revenue</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Net debt</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr"/>
+      <c r="C13" s="3" t="inlineStr"/>
+      <c r="D13" s="3" t="inlineStr"/>
+      <c r="E13" s="3" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Net debt; TTM = MRQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Net debt / EBITDA</t>
+        </is>
+      </c>
+      <c r="B14" s="5">
+        <f>IFERROR(B13/B8,"")</f>
+        <v/>
+      </c>
+      <c r="C14" s="5">
+        <f>IFERROR(C13/C8,"")</f>
+        <v/>
+      </c>
+      <c r="D14" s="5">
+        <f>IFERROR(D13/D8,"")</f>
+        <v/>
+      </c>
+      <c r="E14" s="5">
+        <f>IFERROR(E13/E8,"")</f>
+        <v/>
+      </c>
+      <c r="F14">
+        <f> net debt / EBITDA</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Share count (period-end, M)</t>
+        </is>
+      </c>
+      <c r="B15" s="6">
+        <f>'Balance sheet (annual)'!D3/1e6</f>
+        <v/>
+      </c>
+      <c r="C15" s="6">
+        <f>'Balance sheet (annual)'!C3/1e6</f>
+        <v/>
+      </c>
+      <c r="D15" s="6">
+        <f>'Balance sheet (annual)'!B3/1e6</f>
+        <v/>
+      </c>
+      <c r="E15" s="6">
+        <f>'Balance sheet (quarterly)'!B3/1e6</f>
+        <v/>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>shares ÷ 1e6; TTM = MRQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Share count YoY %</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr"/>
+      <c r="C16" s="4">
+        <f>IFERROR(C15/B15-1,"")</f>
+        <v/>
+      </c>
+      <c r="D16" s="4">
+        <f>IFERROR(D15/C15-1,"")</f>
+        <v/>
+      </c>
+      <c r="E16" s="4">
+        <f>IFERROR(E15/D15-1,"")</f>
+        <v/>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>vs prior period</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1904,13 +2372,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G45"/>
+  <dimension ref="A1:H45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1920,6 +2388,7 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1930,30 +2399,35 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>2025-12-31</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>2025-06-30</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>2025-03-31</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>2024-12-31</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>2024-09-30</t>
         </is>
@@ -1981,6 +2455,7 @@
         <v>0</v>
       </c>
       <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1989,21 +2464,22 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
+        <v>0.148</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>0.219383</v>
       </c>
-      <c r="C3" s="3" t="n">
+      <c r="D3" s="3" t="n">
         <v>0.115</v>
       </c>
-      <c r="D3" s="3" t="n">
+      <c r="E3" s="3" t="n">
         <v>0.21</v>
       </c>
-      <c r="E3" s="3" t="n">
-        <v>0.148</v>
-      </c>
       <c r="F3" s="3" t="n">
-        <v>0.21</v>
+        <v>0.149091</v>
       </c>
       <c r="G3" s="3" t="n"/>
+      <c r="H3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2012,21 +2488,22 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
+        <v>2398000000</v>
+      </c>
+      <c r="C4" s="3" t="n">
         <v>2861000000</v>
       </c>
-      <c r="C4" s="3" t="n">
+      <c r="D4" s="3" t="n">
         <v>2106000000</v>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="E4" s="3" t="n">
         <v>721000000</v>
       </c>
-      <c r="E4" s="3" t="n">
+      <c r="F4" s="3" t="n">
         <v>1587000000</v>
       </c>
-      <c r="F4" s="3" t="n">
-        <v>1694000000</v>
-      </c>
       <c r="G4" s="3" t="n"/>
+      <c r="H4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2035,21 +2512,22 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
+        <v>1372000000</v>
+      </c>
+      <c r="C5" s="3" t="n">
         <v>1620000000</v>
       </c>
-      <c r="C5" s="3" t="n">
+      <c r="D5" s="3" t="n">
         <v>1172000000</v>
       </c>
-      <c r="D5" s="3" t="n">
+      <c r="E5" s="3" t="n">
         <v>768000000</v>
       </c>
-      <c r="E5" s="3" t="n">
+      <c r="F5" s="3" t="n">
         <v>709000000</v>
       </c>
-      <c r="F5" s="3" t="n">
-        <v>482000000</v>
-      </c>
       <c r="G5" s="3" t="n"/>
+      <c r="H5" s="3" t="n"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2058,21 +2536,22 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
+        <v>757000000</v>
+      </c>
+      <c r="C6" s="3" t="n">
         <v>751000000</v>
       </c>
-      <c r="C6" s="3" t="n">
+      <c r="D6" s="3" t="n">
         <v>754000000</v>
       </c>
-      <c r="D6" s="3" t="n">
+      <c r="E6" s="3" t="n">
         <v>757000000</v>
       </c>
-      <c r="E6" s="3" t="n">
+      <c r="F6" s="3" t="n">
         <v>742000000</v>
       </c>
-      <c r="F6" s="3" t="n">
-        <v>786000000</v>
-      </c>
       <c r="G6" s="3" t="n"/>
+      <c r="H6" s="3" t="n"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2081,21 +2560,22 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
+        <v>4370000000</v>
+      </c>
+      <c r="C7" s="3" t="n">
         <v>4239000000</v>
       </c>
-      <c r="C7" s="3" t="n">
+      <c r="D7" s="3" t="n">
         <v>4014000000</v>
       </c>
-      <c r="D7" s="3" t="n">
+      <c r="E7" s="3" t="n">
         <v>4177000000</v>
       </c>
-      <c r="E7" s="3" t="n">
+      <c r="F7" s="3" t="n">
         <v>3276000000</v>
       </c>
-      <c r="F7" s="3" t="n">
-        <v>3322000000</v>
-      </c>
       <c r="G7" s="3" t="n"/>
+      <c r="H7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2104,21 +2584,22 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
+        <v>2398000000</v>
+      </c>
+      <c r="C8" s="3" t="n">
         <v>2861000000</v>
       </c>
-      <c r="C8" s="3" t="n">
+      <c r="D8" s="3" t="n">
         <v>2106000000</v>
       </c>
-      <c r="D8" s="3" t="n">
+      <c r="E8" s="3" t="n">
         <v>721000000</v>
       </c>
-      <c r="E8" s="3" t="n">
+      <c r="F8" s="3" t="n">
         <v>1587000000</v>
       </c>
-      <c r="F8" s="3" t="n">
-        <v>1694000000</v>
-      </c>
       <c r="G8" s="3" t="n"/>
+      <c r="H8" s="3" t="n"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2127,21 +2608,22 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
+        <v>1641000000</v>
+      </c>
+      <c r="C9" s="3" t="n">
         <v>2110000000</v>
       </c>
-      <c r="C9" s="3" t="n">
+      <c r="D9" s="3" t="n">
         <v>1352000000</v>
       </c>
-      <c r="D9" s="3" t="n">
+      <c r="E9" s="3" t="n">
         <v>-36000000</v>
       </c>
-      <c r="E9" s="3" t="n">
+      <c r="F9" s="3" t="n">
         <v>845000000</v>
       </c>
-      <c r="F9" s="3" t="n">
-        <v>908000000</v>
-      </c>
       <c r="G9" s="3" t="n"/>
+      <c r="H9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2150,21 +2632,22 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
+        <v>-37000000</v>
+      </c>
+      <c r="C10" s="3" t="n">
         <v>179000000</v>
       </c>
-      <c r="C10" s="3" t="n">
+      <c r="D10" s="3" t="n">
         <v>-37000000</v>
       </c>
-      <c r="D10" s="3" t="n">
+      <c r="E10" s="3" t="n">
         <v>-38000000</v>
       </c>
-      <c r="E10" s="3" t="n">
+      <c r="F10" s="3" t="n">
         <v>-20000000</v>
       </c>
-      <c r="F10" s="3" t="n">
-        <v>163000000</v>
-      </c>
       <c r="G10" s="3" t="n"/>
+      <c r="H10" s="3" t="n"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2173,21 +2656,22 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
+        <v>37000000</v>
+      </c>
+      <c r="C11" s="3" t="n">
         <v>36000000</v>
       </c>
-      <c r="C11" s="3" t="n">
+      <c r="D11" s="3" t="n">
         <v>37000000</v>
       </c>
-      <c r="D11" s="3" t="n">
+      <c r="E11" s="3" t="n">
         <v>38000000</v>
       </c>
-      <c r="E11" s="3" t="n">
+      <c r="F11" s="3" t="n">
         <v>20000000</v>
       </c>
-      <c r="F11" s="3" t="n">
-        <v>19000000</v>
-      </c>
       <c r="G11" s="3" t="n"/>
+      <c r="H11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2196,21 +2680,22 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
+        <v>1372000000</v>
+      </c>
+      <c r="C12" s="3" t="n">
         <v>1620000000</v>
       </c>
-      <c r="C12" s="3" t="n">
+      <c r="D12" s="3" t="n">
         <v>1172000000</v>
       </c>
-      <c r="D12" s="3" t="n">
+      <c r="E12" s="3" t="n">
         <v>768000000</v>
       </c>
-      <c r="E12" s="3" t="n">
+      <c r="F12" s="3" t="n">
         <v>709000000</v>
       </c>
-      <c r="F12" s="3" t="n">
-        <v>482000000</v>
-      </c>
       <c r="G12" s="3" t="n"/>
+      <c r="H12" s="3" t="n"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2219,21 +2704,22 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
+        <v>1383000000</v>
+      </c>
+      <c r="C13" s="3" t="n">
         <v>1511000000</v>
       </c>
-      <c r="C13" s="3" t="n">
+      <c r="D13" s="3" t="n">
         <v>1243000000</v>
       </c>
-      <c r="D13" s="3" t="n">
+      <c r="E13" s="3" t="n">
         <v>872000000</v>
       </c>
-      <c r="E13" s="3" t="n">
+      <c r="F13" s="3" t="n">
         <v>709000000</v>
       </c>
-      <c r="F13" s="3" t="n">
-        <v>482000000</v>
-      </c>
       <c r="G13" s="3" t="n"/>
+      <c r="H13" s="3" t="n"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2242,21 +2728,22 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
+        <v>8777000000</v>
+      </c>
+      <c r="C14" s="3" t="n">
         <v>8518000000</v>
       </c>
-      <c r="C14" s="3" t="n">
+      <c r="D14" s="3" t="n">
         <v>7976000000</v>
       </c>
-      <c r="D14" s="3" t="n">
+      <c r="E14" s="3" t="n">
         <v>7819000000</v>
       </c>
-      <c r="E14" s="3" t="n">
+      <c r="F14" s="3" t="n">
         <v>6632000000</v>
       </c>
-      <c r="F14" s="3" t="n">
-        <v>6601000000</v>
-      </c>
       <c r="G14" s="3" t="n"/>
+      <c r="H14" s="3" t="n"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2265,21 +2752,22 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
+        <v>1476000000</v>
+      </c>
+      <c r="C15" s="3" t="n">
         <v>1752000000</v>
       </c>
-      <c r="C15" s="3" t="n">
+      <c r="D15" s="3" t="n">
         <v>1270000000</v>
       </c>
-      <c r="D15" s="3" t="n">
+      <c r="E15" s="3" t="n">
         <v>-134000000</v>
       </c>
-      <c r="E15" s="3" t="n">
+      <c r="F15" s="3" t="n">
         <v>806000000</v>
       </c>
-      <c r="F15" s="3" t="n">
-        <v>871000000</v>
-      </c>
       <c r="G15" s="3" t="n"/>
+      <c r="H15" s="3" t="n"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2288,21 +2776,22 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
+        <v>1650000000</v>
+      </c>
+      <c r="C16" s="3" t="n">
         <v>1649000000</v>
       </c>
-      <c r="C16" s="3" t="n">
+      <c r="D16" s="3" t="n">
         <v>1641000000</v>
       </c>
-      <c r="D16" s="3" t="n">
+      <c r="E16" s="3" t="n">
         <v>1630000000</v>
       </c>
-      <c r="E16" s="3" t="n">
+      <c r="F16" s="3" t="n">
         <v>1626000000</v>
       </c>
-      <c r="F16" s="3" t="n">
-        <v>1634000000</v>
-      </c>
       <c r="G16" s="3" t="n"/>
+      <c r="H16" s="3" t="n"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2311,21 +2800,22 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
+        <v>1631000000</v>
+      </c>
+      <c r="C17" s="3" t="n">
         <v>1630000000</v>
       </c>
-      <c r="C17" s="3" t="n">
+      <c r="D17" s="3" t="n">
         <v>1626000000</v>
       </c>
-      <c r="D17" s="3" t="n">
+      <c r="E17" s="3" t="n">
         <v>1623000000</v>
       </c>
-      <c r="E17" s="3" t="n">
+      <c r="F17" s="3" t="n">
         <v>1620000000</v>
       </c>
-      <c r="F17" s="3" t="n">
-        <v>1623000000</v>
-      </c>
       <c r="G17" s="3" t="n"/>
+      <c r="H17" s="3" t="n"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2334,21 +2824,22 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="C18" s="3" t="n">
         <v>0.92</v>
       </c>
-      <c r="C18" s="3" t="n">
+      <c r="D18" s="3" t="n">
         <v>0.75</v>
       </c>
-      <c r="D18" s="3" t="n">
+      <c r="E18" s="3" t="n">
         <v>0.54</v>
       </c>
-      <c r="E18" s="3" t="n">
+      <c r="F18" s="3" t="n">
         <v>0.44</v>
       </c>
-      <c r="F18" s="3" t="n">
-        <v>0.29</v>
-      </c>
       <c r="G18" s="3" t="n"/>
+      <c r="H18" s="3" t="n"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2357,21 +2848,22 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="C19" s="3" t="n">
         <v>0.93</v>
       </c>
-      <c r="C19" s="3" t="n">
+      <c r="D19" s="3" t="n">
         <v>0.76</v>
       </c>
-      <c r="D19" s="3" t="n">
+      <c r="E19" s="3" t="n">
         <v>0.54</v>
       </c>
-      <c r="E19" s="3" t="n">
+      <c r="F19" s="3" t="n">
         <v>0.44</v>
       </c>
-      <c r="F19" s="3" t="n">
-        <v>0.3</v>
-      </c>
       <c r="G19" s="3" t="n"/>
+      <c r="H19" s="3" t="n"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2380,21 +2872,22 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
+        <v>1383000000</v>
+      </c>
+      <c r="C20" s="3" t="n">
         <v>1511000000</v>
       </c>
-      <c r="C20" s="3" t="n">
+      <c r="D20" s="3" t="n">
         <v>1243000000</v>
       </c>
-      <c r="D20" s="3" t="n">
+      <c r="E20" s="3" t="n">
         <v>872000000</v>
       </c>
-      <c r="E20" s="3" t="n">
+      <c r="F20" s="3" t="n">
         <v>709000000</v>
       </c>
-      <c r="F20" s="3" t="n">
-        <v>482000000</v>
-      </c>
       <c r="G20" s="3" t="n"/>
+      <c r="H20" s="3" t="n"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2403,21 +2896,22 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
+        <v>1383000000</v>
+      </c>
+      <c r="C21" s="3" t="n">
         <v>1511000000</v>
       </c>
-      <c r="C21" s="3" t="n">
+      <c r="D21" s="3" t="n">
         <v>1243000000</v>
       </c>
-      <c r="D21" s="3" t="n">
+      <c r="E21" s="3" t="n">
         <v>872000000</v>
       </c>
-      <c r="E21" s="3" t="n">
+      <c r="F21" s="3" t="n">
         <v>709000000</v>
       </c>
-      <c r="F21" s="3" t="n">
-        <v>482000000</v>
-      </c>
       <c r="G21" s="3" t="n"/>
+      <c r="H21" s="3" t="n"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2426,21 +2920,22 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
+        <v>1383000000</v>
+      </c>
+      <c r="C22" s="3" t="n">
         <v>1511000000</v>
       </c>
-      <c r="C22" s="3" t="n">
+      <c r="D22" s="3" t="n">
         <v>1243000000</v>
       </c>
-      <c r="D22" s="3" t="n">
+      <c r="E22" s="3" t="n">
         <v>872000000</v>
       </c>
-      <c r="E22" s="3" t="n">
+      <c r="F22" s="3" t="n">
         <v>709000000</v>
       </c>
-      <c r="F22" s="3" t="n">
-        <v>482000000</v>
-      </c>
       <c r="G22" s="3" t="n"/>
+      <c r="H22" s="3" t="n"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2449,21 +2944,22 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
+        <v>1383000000</v>
+      </c>
+      <c r="C23" s="3" t="n">
         <v>1511000000</v>
       </c>
-      <c r="C23" s="3" t="n">
+      <c r="D23" s="3" t="n">
         <v>1243000000</v>
       </c>
-      <c r="D23" s="3" t="n">
+      <c r="E23" s="3" t="n">
         <v>872000000</v>
       </c>
-      <c r="E23" s="3" t="n">
+      <c r="F23" s="3" t="n">
         <v>709000000</v>
       </c>
-      <c r="F23" s="3" t="n">
-        <v>482000000</v>
-      </c>
       <c r="G23" s="3" t="n"/>
+      <c r="H23" s="3" t="n"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2472,17 +2968,22 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
+        <v>11000000</v>
+      </c>
+      <c r="C24" s="3" t="n">
         <v>-109000000</v>
       </c>
-      <c r="C24" s="3" t="n">
+      <c r="D24" s="3" t="n">
         <v>71000000</v>
       </c>
-      <c r="D24" s="3" t="n">
+      <c r="E24" s="3" t="n">
         <v>104000000</v>
       </c>
-      <c r="E24" s="3" t="n"/>
-      <c r="F24" s="3" t="n"/>
+      <c r="F24" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="G24" s="3" t="n"/>
+      <c r="H24" s="3" t="n"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2491,21 +2992,22 @@
         </is>
       </c>
       <c r="B25" s="3" t="n">
+        <v>1372000000</v>
+      </c>
+      <c r="C25" s="3" t="n">
         <v>1620000000</v>
       </c>
-      <c r="C25" s="3" t="n">
+      <c r="D25" s="3" t="n">
         <v>1172000000</v>
       </c>
-      <c r="D25" s="3" t="n">
+      <c r="E25" s="3" t="n">
         <v>768000000</v>
       </c>
-      <c r="E25" s="3" t="n">
+      <c r="F25" s="3" t="n">
         <v>709000000</v>
       </c>
-      <c r="F25" s="3" t="n">
-        <v>482000000</v>
-      </c>
       <c r="G25" s="3" t="n"/>
+      <c r="H25" s="3" t="n"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2514,21 +3016,22 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
+        <v>6000000</v>
+      </c>
+      <c r="C26" s="3" t="n">
         <v>1000000</v>
       </c>
-      <c r="C26" s="3" t="n">
+      <c r="D26" s="3" t="n">
         <v>10000000</v>
       </c>
-      <c r="D26" s="3" t="n">
+      <c r="E26" s="3" t="n">
         <v>8000000</v>
       </c>
-      <c r="E26" s="3" t="n">
+      <c r="F26" s="3" t="n">
         <v>7000000</v>
       </c>
-      <c r="F26" s="3" t="n">
-        <v>12000000</v>
-      </c>
       <c r="G26" s="3" t="n"/>
+      <c r="H26" s="3" t="n"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2537,21 +3040,22 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
+        <v>238000000</v>
+      </c>
+      <c r="C27" s="3" t="n">
         <v>455000000</v>
       </c>
-      <c r="C27" s="3" t="n">
+      <c r="D27" s="3" t="n">
         <v>153000000</v>
       </c>
-      <c r="D27" s="3" t="n">
+      <c r="E27" s="3" t="n">
         <v>-834000000</v>
       </c>
-      <c r="E27" s="3" t="n">
+      <c r="F27" s="3" t="n">
         <v>123000000</v>
       </c>
-      <c r="F27" s="3" t="n">
-        <v>419000000</v>
-      </c>
       <c r="G27" s="3" t="n"/>
+      <c r="H27" s="3" t="n"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2560,21 +3064,22 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
+        <v>1604000000</v>
+      </c>
+      <c r="C28" s="3" t="n">
         <v>2074000000</v>
       </c>
-      <c r="C28" s="3" t="n">
+      <c r="D28" s="3" t="n">
         <v>1315000000</v>
       </c>
-      <c r="D28" s="3" t="n">
+      <c r="E28" s="3" t="n">
         <v>-74000000</v>
       </c>
-      <c r="E28" s="3" t="n">
+      <c r="F28" s="3" t="n">
         <v>825000000</v>
       </c>
-      <c r="F28" s="3" t="n">
-        <v>889000000</v>
-      </c>
       <c r="G28" s="3" t="n"/>
+      <c r="H28" s="3" t="n"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2583,21 +3088,22 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
+        <v>165000000</v>
+      </c>
+      <c r="C29" s="3" t="n">
         <v>143000000</v>
       </c>
-      <c r="C29" s="3" t="n">
+      <c r="D29" s="3" t="n">
         <v>82000000</v>
       </c>
-      <c r="D29" s="3" t="n">
+      <c r="E29" s="3" t="n">
         <v>98000000</v>
       </c>
-      <c r="E29" s="3" t="n">
+      <c r="F29" s="3" t="n">
         <v>39000000</v>
       </c>
-      <c r="F29" s="3" t="n">
-        <v>-331000000</v>
-      </c>
       <c r="G29" s="3" t="n"/>
+      <c r="H29" s="3" t="n"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2606,21 +3112,22 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
+        <v>165000000</v>
+      </c>
+      <c r="C30" s="3" t="n">
         <v>-223000000</v>
       </c>
-      <c r="C30" s="3" t="n">
+      <c r="D30" s="3" t="n">
         <v>82000000</v>
       </c>
-      <c r="D30" s="3" t="n">
+      <c r="E30" s="3" t="n">
         <v>98000000</v>
       </c>
-      <c r="E30" s="3" t="n">
+      <c r="F30" s="3" t="n">
         <v>39000000</v>
       </c>
-      <c r="F30" s="3" t="n">
-        <v>-147000000</v>
-      </c>
       <c r="G30" s="3" t="n"/>
+      <c r="H30" s="3" t="n"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2629,21 +3136,22 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
+        <v>-37000000</v>
+      </c>
+      <c r="C31" s="3" t="n">
         <v>179000000</v>
       </c>
-      <c r="C31" s="3" t="n">
+      <c r="D31" s="3" t="n">
         <v>-37000000</v>
       </c>
-      <c r="D31" s="3" t="n">
+      <c r="E31" s="3" t="n">
         <v>-38000000</v>
       </c>
-      <c r="E31" s="3" t="n">
+      <c r="F31" s="3" t="n">
         <v>-20000000</v>
       </c>
-      <c r="F31" s="3" t="n">
-        <v>163000000</v>
-      </c>
       <c r="G31" s="3" t="n"/>
+      <c r="H31" s="3" t="n"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2652,21 +3160,22 @@
         </is>
       </c>
       <c r="B32" s="3" t="n">
+        <v>37000000</v>
+      </c>
+      <c r="C32" s="3" t="n">
         <v>36000000</v>
       </c>
-      <c r="C32" s="3" t="n">
+      <c r="D32" s="3" t="n">
         <v>37000000</v>
       </c>
-      <c r="D32" s="3" t="n">
+      <c r="E32" s="3" t="n">
         <v>38000000</v>
       </c>
-      <c r="E32" s="3" t="n">
+      <c r="F32" s="3" t="n">
         <v>20000000</v>
       </c>
-      <c r="F32" s="3" t="n">
-        <v>19000000</v>
-      </c>
       <c r="G32" s="3" t="n"/>
+      <c r="H32" s="3" t="n"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2675,21 +3184,22 @@
         </is>
       </c>
       <c r="B33" s="3" t="n">
+        <v>1476000000</v>
+      </c>
+      <c r="C33" s="3" t="n">
         <v>1752000000</v>
       </c>
-      <c r="C33" s="3" t="n">
+      <c r="D33" s="3" t="n">
         <v>1270000000</v>
       </c>
-      <c r="D33" s="3" t="n">
+      <c r="E33" s="3" t="n">
         <v>-134000000</v>
       </c>
-      <c r="E33" s="3" t="n">
+      <c r="F33" s="3" t="n">
         <v>806000000</v>
       </c>
-      <c r="F33" s="3" t="n">
-        <v>1057000000</v>
-      </c>
       <c r="G33" s="3" t="n"/>
+      <c r="H33" s="3" t="n"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2698,21 +3208,22 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
+        <v>3940000000</v>
+      </c>
+      <c r="C34" s="3" t="n">
         <v>3825000000</v>
       </c>
-      <c r="C34" s="3" t="n">
+      <c r="D34" s="3" t="n">
         <v>3510000000</v>
       </c>
-      <c r="D34" s="3" t="n">
+      <c r="E34" s="3" t="n">
         <v>3193000000</v>
       </c>
-      <c r="E34" s="3" t="n">
+      <c r="F34" s="3" t="n">
         <v>2930000000</v>
       </c>
-      <c r="F34" s="3" t="n">
-        <v>2825000000</v>
-      </c>
       <c r="G34" s="3" t="n"/>
+      <c r="H34" s="3" t="n"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2724,10 +3235,11 @@
       <c r="C35" s="3" t="n"/>
       <c r="D35" s="3" t="n"/>
       <c r="E35" s="3" t="n"/>
-      <c r="F35" s="3" t="n">
+      <c r="F35" s="3" t="n"/>
+      <c r="G35" s="3" t="n">
         <v>-11000000</v>
       </c>
-      <c r="G35" s="3" t="n">
+      <c r="H35" s="3" t="n">
         <v>-14000000</v>
       </c>
     </row>
@@ -2738,21 +3250,22 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
+        <v>290000000</v>
+      </c>
+      <c r="C36" s="3" t="n">
         <v>297000000</v>
       </c>
-      <c r="C36" s="3" t="n">
+      <c r="D36" s="3" t="n">
         <v>302000000</v>
       </c>
-      <c r="D36" s="3" t="n">
+      <c r="E36" s="3" t="n">
         <v>308000000</v>
       </c>
-      <c r="E36" s="3" t="n">
+      <c r="F36" s="3" t="n">
         <v>316000000</v>
       </c>
-      <c r="F36" s="3" t="n">
-        <v>332000000</v>
-      </c>
       <c r="G36" s="3" t="n"/>
+      <c r="H36" s="3" t="n"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2761,21 +3274,22 @@
         </is>
       </c>
       <c r="B37" s="3" t="n">
+        <v>290000000</v>
+      </c>
+      <c r="C37" s="3" t="n">
         <v>297000000</v>
       </c>
-      <c r="C37" s="3" t="n">
+      <c r="D37" s="3" t="n">
         <v>302000000</v>
       </c>
-      <c r="D37" s="3" t="n">
+      <c r="E37" s="3" t="n">
         <v>308000000</v>
       </c>
-      <c r="E37" s="3" t="n">
+      <c r="F37" s="3" t="n">
         <v>316000000</v>
       </c>
-      <c r="F37" s="3" t="n">
-        <v>332000000</v>
-      </c>
       <c r="G37" s="3" t="n"/>
+      <c r="H37" s="3" t="n"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2784,21 +3298,22 @@
         </is>
       </c>
       <c r="B38" s="3" t="n">
+        <v>290000000</v>
+      </c>
+      <c r="C38" s="3" t="n">
         <v>297000000</v>
       </c>
-      <c r="C38" s="3" t="n">
+      <c r="D38" s="3" t="n">
         <v>302000000</v>
       </c>
-      <c r="D38" s="3" t="n">
+      <c r="E38" s="3" t="n">
         <v>308000000</v>
       </c>
-      <c r="E38" s="3" t="n">
+      <c r="F38" s="3" t="n">
         <v>316000000</v>
       </c>
-      <c r="F38" s="3" t="n">
-        <v>332000000</v>
-      </c>
       <c r="G38" s="3" t="n"/>
+      <c r="H38" s="3" t="n"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2807,21 +3322,22 @@
         </is>
       </c>
       <c r="B39" s="3" t="n">
+        <v>290000000</v>
+      </c>
+      <c r="C39" s="3" t="n">
         <v>297000000</v>
       </c>
-      <c r="C39" s="3" t="n">
+      <c r="D39" s="3" t="n">
         <v>302000000</v>
       </c>
-      <c r="D39" s="3" t="n">
+      <c r="E39" s="3" t="n">
         <v>308000000</v>
       </c>
-      <c r="E39" s="3" t="n">
+      <c r="F39" s="3" t="n">
         <v>316000000</v>
       </c>
-      <c r="F39" s="3" t="n">
-        <v>332000000</v>
-      </c>
       <c r="G39" s="3" t="n"/>
+      <c r="H39" s="3" t="n"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2830,21 +3346,22 @@
         </is>
       </c>
       <c r="B40" s="3" t="n">
+        <v>2397000000</v>
+      </c>
+      <c r="C40" s="3" t="n">
         <v>2330000000</v>
       </c>
-      <c r="C40" s="3" t="n">
+      <c r="D40" s="3" t="n">
         <v>2139000000</v>
       </c>
-      <c r="D40" s="3" t="n">
+      <c r="E40" s="3" t="n">
         <v>1894000000</v>
       </c>
-      <c r="E40" s="3" t="n">
+      <c r="F40" s="3" t="n">
         <v>1728000000</v>
       </c>
-      <c r="F40" s="3" t="n">
-        <v>1712000000</v>
-      </c>
       <c r="G40" s="3" t="n"/>
+      <c r="H40" s="3" t="n"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2853,21 +3370,22 @@
         </is>
       </c>
       <c r="B41" s="3" t="n">
+        <v>1253000000</v>
+      </c>
+      <c r="C41" s="3" t="n">
         <v>1198000000</v>
       </c>
-      <c r="C41" s="3" t="n">
+      <c r="D41" s="3" t="n">
         <v>1069000000</v>
       </c>
-      <c r="D41" s="3" t="n">
+      <c r="E41" s="3" t="n">
         <v>991000000</v>
       </c>
-      <c r="E41" s="3" t="n">
+      <c r="F41" s="3" t="n">
         <v>886000000</v>
       </c>
-      <c r="F41" s="3" t="n">
-        <v>792000000</v>
-      </c>
       <c r="G41" s="3" t="n"/>
+      <c r="H41" s="3" t="n"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2876,21 +3394,22 @@
         </is>
       </c>
       <c r="B42" s="3" t="n">
+        <v>5416000000</v>
+      </c>
+      <c r="C42" s="3" t="n">
         <v>5577000000</v>
       </c>
-      <c r="C42" s="3" t="n">
+      <c r="D42" s="3" t="n">
         <v>4780000000</v>
       </c>
-      <c r="D42" s="3" t="n">
+      <c r="E42" s="3" t="n">
         <v>3059000000</v>
       </c>
-      <c r="E42" s="3" t="n">
+      <c r="F42" s="3" t="n">
         <v>3736000000</v>
       </c>
-      <c r="F42" s="3" t="n">
-        <v>3882000000</v>
-      </c>
       <c r="G42" s="3" t="n"/>
+      <c r="H42" s="3" t="n"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2899,21 +3418,22 @@
         </is>
       </c>
       <c r="B43" s="3" t="n">
+        <v>4837000000</v>
+      </c>
+      <c r="C43" s="3" t="n">
         <v>4693000000</v>
       </c>
-      <c r="C43" s="3" t="n">
+      <c r="D43" s="3" t="n">
         <v>4466000000</v>
       </c>
-      <c r="D43" s="3" t="n">
+      <c r="E43" s="3" t="n">
         <v>4626000000</v>
       </c>
-      <c r="E43" s="3" t="n">
+      <c r="F43" s="3" t="n">
         <v>3702000000</v>
       </c>
-      <c r="F43" s="3" t="n">
-        <v>3776000000</v>
-      </c>
       <c r="G43" s="3" t="n"/>
+      <c r="H43" s="3" t="n"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2922,21 +3442,22 @@
         </is>
       </c>
       <c r="B44" s="3" t="n">
+        <v>10253000000</v>
+      </c>
+      <c r="C44" s="3" t="n">
         <v>10270000000</v>
       </c>
-      <c r="C44" s="3" t="n">
+      <c r="D44" s="3" t="n">
         <v>9246000000</v>
       </c>
-      <c r="D44" s="3" t="n">
+      <c r="E44" s="3" t="n">
         <v>7685000000</v>
       </c>
-      <c r="E44" s="3" t="n">
+      <c r="F44" s="3" t="n">
         <v>7438000000</v>
       </c>
-      <c r="F44" s="3" t="n">
-        <v>7658000000</v>
-      </c>
       <c r="G44" s="3" t="n"/>
+      <c r="H44" s="3" t="n"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2945,28 +3466,29 @@
         </is>
       </c>
       <c r="B45" s="3" t="n">
+        <v>10253000000</v>
+      </c>
+      <c r="C45" s="3" t="n">
         <v>10270000000</v>
       </c>
-      <c r="C45" s="3" t="n">
+      <c r="D45" s="3" t="n">
         <v>9246000000</v>
       </c>
-      <c r="D45" s="3" t="n">
+      <c r="E45" s="3" t="n">
         <v>7685000000</v>
       </c>
-      <c r="E45" s="3" t="n">
+      <c r="F45" s="3" t="n">
         <v>7438000000</v>
       </c>
-      <c r="F45" s="3" t="n">
-        <v>7658000000</v>
-      </c>
       <c r="G45" s="3" t="n"/>
+      <c r="H45" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4498,7 +5020,1687 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H70"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>2024-12-31</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Treasury Shares Number</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>67000000</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>65000000</v>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>65000000</v>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>62000000</v>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>65000000</v>
+      </c>
+      <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Ordinary Shares Number</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>1630410843</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>1630000000</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>1628000000</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>1622000000</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>1624335849</v>
+      </c>
+      <c r="G3" s="3" t="n"/>
+      <c r="H3" s="3" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Share Issued</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>1697410843</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>1695000000</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>1693000000</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>1684000000</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>1689335849</v>
+      </c>
+      <c r="G4" s="3" t="n"/>
+      <c r="H4" s="3" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Total Debt</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>3871000000</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>3847000000</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>3870000000</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>3886000000</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>4731000000</v>
+      </c>
+      <c r="G5" s="3" t="n"/>
+      <c r="H5" s="3" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Tangible Book Value</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>22964000000</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>21168000000</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>18457000000</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>16770000000</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>14679000000</v>
+      </c>
+      <c r="G6" s="3" t="n"/>
+      <c r="H6" s="3" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Invested Capital</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>67686000000</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>66221000000</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>64010000000</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>62883000000</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>62045000000</v>
+      </c>
+      <c r="G7" s="3" t="n"/>
+      <c r="H7" s="3" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Working Capital</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>18122000000</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>17492000000</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>15300000000</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>14676000000</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>13892000000</v>
+      </c>
+      <c r="G8" s="3" t="n"/>
+      <c r="H8" s="3" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Net Tangible Assets</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>22964000000</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>21168000000</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>18457000000</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>16770000000</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>14679000000</v>
+      </c>
+      <c r="G9" s="3" t="n"/>
+      <c r="H9" s="3" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Capital Lease Obligations</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>647000000</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>625000000</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>650000000</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>668000000</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>567000000</v>
+      </c>
+      <c r="G10" s="3" t="n"/>
+      <c r="H10" s="3" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Common Stock Equity</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>64462000000</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>62999000000</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>60790000000</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>59665000000</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>57881000000</v>
+      </c>
+      <c r="G11" s="3" t="n"/>
+      <c r="H11" s="3" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Total Capitalization</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>66812000000</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>65347000000</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>63137000000</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>62883000000</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>61098000000</v>
+      </c>
+      <c r="G12" s="3" t="n"/>
+      <c r="H12" s="3" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Total Equity Gross Minority Interest</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>64462000000</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>62999000000</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>60790000000</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>59665000000</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>57881000000</v>
+      </c>
+      <c r="G13" s="3" t="n"/>
+      <c r="H13" s="3" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Stockholders Equity</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n">
+        <v>64462000000</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>62999000000</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>60790000000</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>59665000000</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>57881000000</v>
+      </c>
+      <c r="G14" s="3" t="n"/>
+      <c r="H14" s="3" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Gains Losses Not Affecting Retained Earnings</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>-72000000</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>-3000000</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>-13000000</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>-40000000</v>
+      </c>
+      <c r="G15" s="3" t="n"/>
+      <c r="H15" s="3" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Other Equity Adjustments</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>-72000000</v>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>-3000000</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>-13000000</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>-40000000</v>
+      </c>
+      <c r="G16" s="3" t="n"/>
+      <c r="H16" s="3" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Treasury Stock</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>7421000000</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>7079000000</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>7059000000</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>6535000000</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>6899000000</v>
+      </c>
+      <c r="G17" s="3" t="n"/>
+      <c r="H17" s="3" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Retained Earnings</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="n">
+        <v>8082000000</v>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>6699000000</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>5188000000</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>3945000000</v>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>3073000000</v>
+      </c>
+      <c r="G18" s="3" t="n"/>
+      <c r="H18" s="3" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Additional Paid In Capital</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>63856000000</v>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>63365000000</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>62657000000</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>62228000000</v>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>61730000000</v>
+      </c>
+      <c r="G19" s="3" t="n"/>
+      <c r="H19" s="3" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Capital Stock</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>17000000</v>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>17000000</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>17000000</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>17000000</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>17000000</v>
+      </c>
+      <c r="G20" s="3" t="n"/>
+      <c r="H20" s="3" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Common Stock</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>17000000</v>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>17000000</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>17000000</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>17000000</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>17000000</v>
+      </c>
+      <c r="G21" s="3" t="n"/>
+      <c r="H21" s="3" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Total Liabilities Net Minority Interest</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>15180000000</v>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>13927000000</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>16101000000</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>15155000000</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>13669000000</v>
+      </c>
+      <c r="G22" s="3" t="n"/>
+      <c r="H22" s="3" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Total Non Current Liabilities Net Minority Interest</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>4674000000</v>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>4472000000</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>4401000000</v>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>5312000000</v>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>5966000000</v>
+      </c>
+      <c r="G23" s="3" t="n"/>
+      <c r="H23" s="3" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Other Non Current Liabilities</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>1370000000</v>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>1186000000</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>1078000000</v>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>1085000000</v>
+      </c>
+      <c r="F24" s="3" t="n">
+        <v>1839000000</v>
+      </c>
+      <c r="G24" s="3" t="n"/>
+      <c r="H24" s="3" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Liabilities</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>307000000</v>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>313000000</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>326000000</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>341000000</v>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>343000000</v>
+      </c>
+      <c r="G25" s="3" t="n"/>
+      <c r="H25" s="3" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Taxes Liabilities</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="n">
+        <v>307000000</v>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>313000000</v>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>326000000</v>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>341000000</v>
+      </c>
+      <c r="F26" s="3" t="n">
+        <v>343000000</v>
+      </c>
+      <c r="G26" s="3" t="n"/>
+      <c r="H26" s="3" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Long Term Debt And Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="n">
+        <v>2997000000</v>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>2973000000</v>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>2997000000</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>3886000000</v>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>3784000000</v>
+      </c>
+      <c r="G27" s="3" t="n"/>
+      <c r="H27" s="3" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Long Term Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="n">
+        <v>647000000</v>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>625000000</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>650000000</v>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>668000000</v>
+      </c>
+      <c r="F28" s="3" t="n">
+        <v>567000000</v>
+      </c>
+      <c r="G28" s="3" t="n"/>
+      <c r="H28" s="3" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Long Term Debt</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="n">
+        <v>2350000000</v>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>2348000000</v>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>2347000000</v>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>3218000000</v>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>3217000000</v>
+      </c>
+      <c r="G29" s="3" t="n"/>
+      <c r="H29" s="3" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Current Liabilities</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="n">
+        <v>10506000000</v>
+      </c>
+      <c r="C30" s="3" t="n">
+        <v>9455000000</v>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>11700000000</v>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>9843000000</v>
+      </c>
+      <c r="F30" s="3" t="n">
+        <v>7703000000</v>
+      </c>
+      <c r="G30" s="3" t="n"/>
+      <c r="H30" s="3" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Other Current Liabilities</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="n">
+        <v>850000000</v>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>402000000</v>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>2232000000</v>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>2284000000</v>
+      </c>
+      <c r="F31" s="3" t="n">
+        <v>674000000</v>
+      </c>
+      <c r="G31" s="3" t="n"/>
+      <c r="H31" s="3" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Current Debt And Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="n">
+        <v>874000000</v>
+      </c>
+      <c r="C32" s="3" t="n">
+        <v>874000000</v>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>873000000</v>
+      </c>
+      <c r="E32" s="3" t="n"/>
+      <c r="F32" s="3" t="n">
+        <v>947000000</v>
+      </c>
+      <c r="G32" s="3" t="n"/>
+      <c r="H32" s="3" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Current Debt</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="n">
+        <v>874000000</v>
+      </c>
+      <c r="C33" s="3" t="n">
+        <v>874000000</v>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>873000000</v>
+      </c>
+      <c r="E33" s="3" t="n"/>
+      <c r="F33" s="3" t="n">
+        <v>947000000</v>
+      </c>
+      <c r="G33" s="3" t="n"/>
+      <c r="H33" s="3" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Other Current Borrowings</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="n">
+        <v>874000000</v>
+      </c>
+      <c r="C34" s="3" t="n">
+        <v>874000000</v>
+      </c>
+      <c r="D34" s="3" t="n"/>
+      <c r="E34" s="3" t="n"/>
+      <c r="F34" s="3" t="n"/>
+      <c r="G34" s="3" t="n"/>
+      <c r="H34" s="3" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Pensionand Other Post Retirement Benefit Plans Current</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="n">
+        <v>1280000000</v>
+      </c>
+      <c r="C35" s="3" t="n">
+        <v>1645000000</v>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>1425000000</v>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>948000000</v>
+      </c>
+      <c r="F35" s="3" t="n">
+        <v>872000000</v>
+      </c>
+      <c r="G35" s="3" t="n"/>
+      <c r="H35" s="3" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Payables And Accrued Expenses</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="n">
+        <v>7502000000</v>
+      </c>
+      <c r="C36" s="3" t="n">
+        <v>6534000000</v>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>7170000000</v>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>6611000000</v>
+      </c>
+      <c r="F36" s="3" t="n">
+        <v>5210000000</v>
+      </c>
+      <c r="G36" s="3" t="n"/>
+      <c r="H36" s="3" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Current Accrued Expenses</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="n">
+        <v>4505000000</v>
+      </c>
+      <c r="C37" s="3" t="n">
+        <v>3605000000</v>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v>3687000000</v>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>3531000000</v>
+      </c>
+      <c r="F37" s="3" t="n">
+        <v>3004000000</v>
+      </c>
+      <c r="G37" s="3" t="n"/>
+      <c r="H37" s="3" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Payables</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="n">
+        <v>2997000000</v>
+      </c>
+      <c r="C38" s="3" t="n">
+        <v>2929000000</v>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v>3483000000</v>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>3080000000</v>
+      </c>
+      <c r="F38" s="3" t="n">
+        <v>2206000000</v>
+      </c>
+      <c r="G38" s="3" t="n"/>
+      <c r="H38" s="3" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Dueto Related Parties Current</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="n"/>
+      <c r="C39" s="3" t="n"/>
+      <c r="D39" s="3" t="n"/>
+      <c r="E39" s="3" t="n"/>
+      <c r="F39" s="3" t="n"/>
+      <c r="G39" s="3" t="n">
+        <v>476000000</v>
+      </c>
+      <c r="H39" s="3" t="n">
+        <v>461000000</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Accounts Payable</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="n">
+        <v>2997000000</v>
+      </c>
+      <c r="C40" s="3" t="n">
+        <v>2929000000</v>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v>3483000000</v>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>3080000000</v>
+      </c>
+      <c r="F40" s="3" t="n">
+        <v>2206000000</v>
+      </c>
+      <c r="G40" s="3" t="n"/>
+      <c r="H40" s="3" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Total Assets</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="n">
+        <v>79642000000</v>
+      </c>
+      <c r="C41" s="3" t="n">
+        <v>76926000000</v>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v>76891000000</v>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>74820000000</v>
+      </c>
+      <c r="F41" s="3" t="n">
+        <v>71550000000</v>
+      </c>
+      <c r="G41" s="3" t="n"/>
+      <c r="H41" s="3" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Total Non Current Assets</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="n">
+        <v>51014000000</v>
+      </c>
+      <c r="C42" s="3" t="n">
+        <v>49979000000</v>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>49891000000</v>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>50301000000</v>
+      </c>
+      <c r="F42" s="3" t="n">
+        <v>49955000000</v>
+      </c>
+      <c r="G42" s="3" t="n"/>
+      <c r="H42" s="3" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Other Non Current Assets</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="n">
+        <v>6317000000</v>
+      </c>
+      <c r="C43" s="3" t="n">
+        <v>5452000000</v>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>4720000000</v>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>4418000000</v>
+      </c>
+      <c r="F43" s="3" t="n">
+        <v>3987000000</v>
+      </c>
+      <c r="G43" s="3" t="n"/>
+      <c r="H43" s="3" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Assets</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="n">
+        <v>476000000</v>
+      </c>
+      <c r="C44" s="3" t="n">
+        <v>384000000</v>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>633000000</v>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>860000000</v>
+      </c>
+      <c r="F44" s="3" t="n">
+        <v>845000000</v>
+      </c>
+      <c r="G44" s="3" t="n"/>
+      <c r="H44" s="3" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Taxes Assets</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="n">
+        <v>476000000</v>
+      </c>
+      <c r="C45" s="3" t="n">
+        <v>384000000</v>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v>633000000</v>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>860000000</v>
+      </c>
+      <c r="F45" s="3" t="n">
+        <v>845000000</v>
+      </c>
+      <c r="G45" s="3" t="n"/>
+      <c r="H45" s="3" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Investments And Advances</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="n"/>
+      <c r="C46" s="3" t="n"/>
+      <c r="D46" s="3" t="n"/>
+      <c r="E46" s="3" t="n"/>
+      <c r="F46" s="3" t="n"/>
+      <c r="G46" s="3" t="n">
+        <v>149000000</v>
+      </c>
+      <c r="H46" s="3" t="n">
+        <v>137000000</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Long Term Equity Investment</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="n"/>
+      <c r="C47" s="3" t="n"/>
+      <c r="D47" s="3" t="n"/>
+      <c r="E47" s="3" t="n"/>
+      <c r="F47" s="3" t="n"/>
+      <c r="G47" s="3" t="n">
+        <v>149000000</v>
+      </c>
+      <c r="H47" s="3" t="n">
+        <v>137000000</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Goodwill And Other Intangible Assets</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="n">
+        <v>41498000000</v>
+      </c>
+      <c r="C48" s="3" t="n">
+        <v>41831000000</v>
+      </c>
+      <c r="D48" s="3" t="n">
+        <v>42333000000</v>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>42895000000</v>
+      </c>
+      <c r="F48" s="3" t="n">
+        <v>43202000000</v>
+      </c>
+      <c r="G48" s="3" t="n"/>
+      <c r="H48" s="3" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Other Intangible Assets</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="n">
+        <v>16154000000</v>
+      </c>
+      <c r="C49" s="3" t="n">
+        <v>16705000000</v>
+      </c>
+      <c r="D49" s="3" t="n">
+        <v>17250000000</v>
+      </c>
+      <c r="E49" s="3" t="n">
+        <v>17812000000</v>
+      </c>
+      <c r="F49" s="3" t="n">
+        <v>18363000000</v>
+      </c>
+      <c r="G49" s="3" t="n"/>
+      <c r="H49" s="3" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Goodwill</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="n">
+        <v>25344000000</v>
+      </c>
+      <c r="C50" s="3" t="n">
+        <v>25126000000</v>
+      </c>
+      <c r="D50" s="3" t="n">
+        <v>25083000000</v>
+      </c>
+      <c r="E50" s="3" t="n">
+        <v>25083000000</v>
+      </c>
+      <c r="F50" s="3" t="n">
+        <v>24839000000</v>
+      </c>
+      <c r="G50" s="3" t="n"/>
+      <c r="H50" s="3" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Net PPE</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="n">
+        <v>2723000000</v>
+      </c>
+      <c r="C51" s="3" t="n">
+        <v>2312000000</v>
+      </c>
+      <c r="D51" s="3" t="n">
+        <v>2205000000</v>
+      </c>
+      <c r="E51" s="3" t="n">
+        <v>2128000000</v>
+      </c>
+      <c r="F51" s="3" t="n">
+        <v>1921000000</v>
+      </c>
+      <c r="G51" s="3" t="n"/>
+      <c r="H51" s="3" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Accumulated Depreciation</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="n">
+        <v>-2752000000</v>
+      </c>
+      <c r="C52" s="3" t="n">
+        <v>-2616000000</v>
+      </c>
+      <c r="D52" s="3" t="n">
+        <v>-2523000000</v>
+      </c>
+      <c r="E52" s="3" t="n">
+        <v>-2434000000</v>
+      </c>
+      <c r="F52" s="3" t="n">
+        <v>-2269000000</v>
+      </c>
+      <c r="G52" s="3" t="n"/>
+      <c r="H52" s="3" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross PPE</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="n">
+        <v>5475000000</v>
+      </c>
+      <c r="C53" s="3" t="n">
+        <v>4928000000</v>
+      </c>
+      <c r="D53" s="3" t="n">
+        <v>4728000000</v>
+      </c>
+      <c r="E53" s="3" t="n">
+        <v>4562000000</v>
+      </c>
+      <c r="F53" s="3" t="n">
+        <v>4190000000</v>
+      </c>
+      <c r="G53" s="3" t="n"/>
+      <c r="H53" s="3" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Construction In Progress</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="n">
+        <v>646000000</v>
+      </c>
+      <c r="C54" s="3" t="n">
+        <v>508000000</v>
+      </c>
+      <c r="D54" s="3" t="n">
+        <v>590000000</v>
+      </c>
+      <c r="E54" s="3" t="n">
+        <v>575000000</v>
+      </c>
+      <c r="F54" s="3" t="n">
+        <v>445000000</v>
+      </c>
+      <c r="G54" s="3" t="n"/>
+      <c r="H54" s="3" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Other Properties</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="n">
+        <v>3795000000</v>
+      </c>
+      <c r="C55" s="3" t="n">
+        <v>3453000000</v>
+      </c>
+      <c r="D55" s="3" t="n">
+        <v>3183000000</v>
+      </c>
+      <c r="E55" s="3" t="n">
+        <v>3065000000</v>
+      </c>
+      <c r="F55" s="3" t="n">
+        <v>2864000000</v>
+      </c>
+      <c r="G55" s="3" t="n"/>
+      <c r="H55" s="3" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Properties</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="n">
+        <v>1034000000</v>
+      </c>
+      <c r="C56" s="3" t="n">
+        <v>967000000</v>
+      </c>
+      <c r="D56" s="3" t="n">
+        <v>955000000</v>
+      </c>
+      <c r="E56" s="3" t="n">
+        <v>922000000</v>
+      </c>
+      <c r="F56" s="3" t="n">
+        <v>881000000</v>
+      </c>
+      <c r="G56" s="3" t="n"/>
+      <c r="H56" s="3" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Current Assets</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="n">
+        <v>28628000000</v>
+      </c>
+      <c r="C57" s="3" t="n">
+        <v>26947000000</v>
+      </c>
+      <c r="D57" s="3" t="n">
+        <v>27000000000</v>
+      </c>
+      <c r="E57" s="3" t="n">
+        <v>24519000000</v>
+      </c>
+      <c r="F57" s="3" t="n">
+        <v>21595000000</v>
+      </c>
+      <c r="G57" s="3" t="n"/>
+      <c r="H57" s="3" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Other Current Assets</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="n">
+        <v>2201000000</v>
+      </c>
+      <c r="C58" s="3" t="n">
+        <v>2160000000</v>
+      </c>
+      <c r="D58" s="3" t="n">
+        <v>1941000000</v>
+      </c>
+      <c r="E58" s="3" t="n">
+        <v>1963000000</v>
+      </c>
+      <c r="F58" s="3" t="n">
+        <v>1583000000</v>
+      </c>
+      <c r="G58" s="3" t="n"/>
+      <c r="H58" s="3" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Assets Held For Sale Current</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="n"/>
+      <c r="C59" s="3" t="n"/>
+      <c r="D59" s="3" t="n">
+        <v>3990000000</v>
+      </c>
+      <c r="E59" s="3" t="n">
+        <v>4326000000</v>
+      </c>
+      <c r="F59" s="3" t="n"/>
+      <c r="G59" s="3" t="n"/>
+      <c r="H59" s="3" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Inventory</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="n">
+        <v>8045000000</v>
+      </c>
+      <c r="C60" s="3" t="n">
+        <v>7920000000</v>
+      </c>
+      <c r="D60" s="3" t="n">
+        <v>7313000000</v>
+      </c>
+      <c r="E60" s="3" t="n">
+        <v>6677000000</v>
+      </c>
+      <c r="F60" s="3" t="n">
+        <v>6416000000</v>
+      </c>
+      <c r="G60" s="3" t="n"/>
+      <c r="H60" s="3" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Finished Goods</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="n">
+        <v>2545000000</v>
+      </c>
+      <c r="C61" s="3" t="n">
+        <v>2243000000</v>
+      </c>
+      <c r="D61" s="3" t="n">
+        <v>2236000000</v>
+      </c>
+      <c r="E61" s="3" t="n">
+        <v>1871000000</v>
+      </c>
+      <c r="F61" s="3" t="n">
+        <v>1358000000</v>
+      </c>
+      <c r="G61" s="3" t="n"/>
+      <c r="H61" s="3" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Work In Process</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="n">
+        <v>4748000000</v>
+      </c>
+      <c r="C62" s="3" t="n">
+        <v>4768000000</v>
+      </c>
+      <c r="D62" s="3" t="n">
+        <v>4401000000</v>
+      </c>
+      <c r="E62" s="3" t="n">
+        <v>4167000000</v>
+      </c>
+      <c r="F62" s="3" t="n">
+        <v>4498000000</v>
+      </c>
+      <c r="G62" s="3" t="n"/>
+      <c r="H62" s="3" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Raw Materials</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="n">
+        <v>752000000</v>
+      </c>
+      <c r="C63" s="3" t="n">
+        <v>909000000</v>
+      </c>
+      <c r="D63" s="3" t="n">
+        <v>676000000</v>
+      </c>
+      <c r="E63" s="3" t="n">
+        <v>639000000</v>
+      </c>
+      <c r="F63" s="3" t="n">
+        <v>560000000</v>
+      </c>
+      <c r="G63" s="3" t="n"/>
+      <c r="H63" s="3" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Receivables</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="n">
+        <v>6035000000</v>
+      </c>
+      <c r="C64" s="3" t="n">
+        <v>6315000000</v>
+      </c>
+      <c r="D64" s="3" t="n">
+        <v>6513000000</v>
+      </c>
+      <c r="E64" s="3" t="n">
+        <v>5686000000</v>
+      </c>
+      <c r="F64" s="3" t="n">
+        <v>6286000000</v>
+      </c>
+      <c r="G64" s="3" t="n"/>
+      <c r="H64" s="3" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Other Receivables</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="n"/>
+      <c r="C65" s="3" t="n"/>
+      <c r="D65" s="3" t="n">
+        <v>312000000</v>
+      </c>
+      <c r="E65" s="3" t="n">
+        <v>571000000</v>
+      </c>
+      <c r="F65" s="3" t="n">
+        <v>843000000</v>
+      </c>
+      <c r="G65" s="3" t="n">
+        <v>628000000</v>
+      </c>
+      <c r="H65" s="3" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Duefrom Related Parties Current</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="n"/>
+      <c r="C66" s="3" t="n"/>
+      <c r="D66" s="3" t="n"/>
+      <c r="E66" s="3" t="n"/>
+      <c r="F66" s="3" t="n"/>
+      <c r="G66" s="3" t="n">
+        <v>113000000</v>
+      </c>
+      <c r="H66" s="3" t="n">
+        <v>29000000</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="n">
+        <v>6035000000</v>
+      </c>
+      <c r="C67" s="3" t="n">
+        <v>6315000000</v>
+      </c>
+      <c r="D67" s="3" t="n">
+        <v>6201000000</v>
+      </c>
+      <c r="E67" s="3" t="n">
+        <v>5115000000</v>
+      </c>
+      <c r="F67" s="3" t="n">
+        <v>5443000000</v>
+      </c>
+      <c r="G67" s="3" t="n"/>
+      <c r="H67" s="3" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Cash Cash Equivalents And Short Term Investments</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="n">
+        <v>12347000000</v>
+      </c>
+      <c r="C68" s="3" t="n">
+        <v>10552000000</v>
+      </c>
+      <c r="D68" s="3" t="n">
+        <v>7243000000</v>
+      </c>
+      <c r="E68" s="3" t="n">
+        <v>5867000000</v>
+      </c>
+      <c r="F68" s="3" t="n">
+        <v>7310000000</v>
+      </c>
+      <c r="G68" s="3" t="n"/>
+      <c r="H68" s="3" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Other Short Term Investments</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="n">
+        <v>6762000000</v>
+      </c>
+      <c r="C69" s="3" t="n">
+        <v>5013000000</v>
+      </c>
+      <c r="D69" s="3" t="n">
+        <v>2435000000</v>
+      </c>
+      <c r="E69" s="3" t="n">
+        <v>1425000000</v>
+      </c>
+      <c r="F69" s="3" t="n">
+        <v>1261000000</v>
+      </c>
+      <c r="G69" s="3" t="n"/>
+      <c r="H69" s="3" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Cash And Cash Equivalents</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="n">
+        <v>5585000000</v>
+      </c>
+      <c r="C70" s="3" t="n">
+        <v>5539000000</v>
+      </c>
+      <c r="D70" s="3" t="n">
+        <v>4808000000</v>
+      </c>
+      <c r="E70" s="3" t="n">
+        <v>4442000000</v>
+      </c>
+      <c r="F70" s="3" t="n">
+        <v>6049000000</v>
+      </c>
+      <c r="G70" s="3" t="n"/>
+      <c r="H70" s="3" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5750,13 +7952,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G56"/>
+  <dimension ref="A1:H58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5766,6 +7968,7 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5776,30 +7979,35 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>2025-12-31</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>2025-06-30</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>2025-03-31</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>2024-12-31</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>2024-09-30</t>
         </is>
@@ -5812,21 +8020,22 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
+        <v>2566000000</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>2378000000</v>
       </c>
-      <c r="C2" s="3" t="n">
+      <c r="D2" s="3" t="n">
         <v>1901000000</v>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="E2" s="3" t="n">
         <v>1729000000</v>
       </c>
-      <c r="E2" s="3" t="n">
+      <c r="F2" s="3" t="n">
         <v>727000000</v>
       </c>
-      <c r="F2" s="3" t="n">
-        <v>1091000000</v>
-      </c>
       <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -5835,21 +8044,22 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
+        <v>-355000000</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>-160000000</v>
       </c>
-      <c r="C3" s="3" t="n">
+      <c r="D3" s="3" t="n">
         <v>-460000000</v>
       </c>
-      <c r="D3" s="3" t="n">
+      <c r="E3" s="3" t="n">
         <v>-524000000</v>
       </c>
-      <c r="E3" s="3" t="n">
+      <c r="F3" s="3" t="n">
         <v>-779000000</v>
       </c>
-      <c r="F3" s="3" t="n">
-        <v>-298000000</v>
-      </c>
       <c r="G3" s="3" t="n"/>
+      <c r="H3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -5857,20 +8067,21 @@
           <t>Repayment Of Debt</t>
         </is>
       </c>
-      <c r="B4" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="B4" s="3" t="n"/>
       <c r="C4" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D4" s="3" t="n"/>
+      <c r="D4" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="E4" s="3" t="n"/>
-      <c r="F4" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="F4" s="3" t="n"/>
       <c r="G4" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="H4" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -5888,10 +8099,13 @@
         <v>0</v>
       </c>
       <c r="E5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="3" t="n">
         <v>2441000000</v>
       </c>
-      <c r="F5" s="3" t="n"/>
       <c r="G5" s="3" t="n"/>
+      <c r="H5" s="3" t="n"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -5900,21 +8114,22 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
+        <v>-389000000</v>
+      </c>
+      <c r="C6" s="3" t="n">
         <v>-222000000</v>
       </c>
-      <c r="C6" s="3" t="n">
+      <c r="D6" s="3" t="n">
         <v>-258000000</v>
       </c>
-      <c r="D6" s="3" t="n">
+      <c r="E6" s="3" t="n">
         <v>-282000000</v>
       </c>
-      <c r="E6" s="3" t="n">
+      <c r="F6" s="3" t="n">
         <v>-212000000</v>
       </c>
-      <c r="F6" s="3" t="n">
-        <v>-208000000</v>
-      </c>
       <c r="G6" s="3" t="n"/>
+      <c r="H6" s="3" t="n"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -5922,20 +8137,23 @@
           <t>Income Tax Paid Supplemental Data</t>
         </is>
       </c>
-      <c r="B7" s="3" t="n"/>
-      <c r="C7" s="3" t="n"/>
+      <c r="B7" s="3" t="n">
+        <v>30000000</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>66000000</v>
+      </c>
       <c r="D7" s="3" t="n">
+        <v>58000000</v>
+      </c>
+      <c r="E7" s="3" t="n">
         <v>632000000</v>
       </c>
-      <c r="E7" s="3" t="n">
+      <c r="F7" s="3" t="n">
         <v>128000000</v>
       </c>
-      <c r="F7" s="3" t="n">
-        <v>375000000</v>
-      </c>
-      <c r="G7" s="3" t="n">
-        <v>700000000</v>
-      </c>
+      <c r="G7" s="3" t="n"/>
+      <c r="H7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -5944,21 +8162,22 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
+        <v>5596000000</v>
+      </c>
+      <c r="C8" s="3" t="n">
         <v>5556000000</v>
       </c>
-      <c r="C8" s="3" t="n">
+      <c r="D8" s="3" t="n">
         <v>4825000000</v>
       </c>
-      <c r="D8" s="3" t="n">
+      <c r="E8" s="3" t="n">
         <v>4453000000</v>
       </c>
-      <c r="E8" s="3" t="n">
+      <c r="F8" s="3" t="n">
         <v>6059000000</v>
       </c>
-      <c r="F8" s="3" t="n">
-        <v>3811000000</v>
-      </c>
       <c r="G8" s="3" t="n"/>
+      <c r="H8" s="3" t="n"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -5967,21 +8186,22 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
+        <v>5556000000</v>
+      </c>
+      <c r="C9" s="3" t="n">
         <v>4825000000</v>
       </c>
-      <c r="C9" s="3" t="n">
+      <c r="D9" s="3" t="n">
         <v>4453000000</v>
       </c>
-      <c r="D9" s="3" t="n">
+      <c r="E9" s="3" t="n">
         <v>6059000000</v>
       </c>
-      <c r="E9" s="3" t="n">
+      <c r="F9" s="3" t="n">
         <v>3811000000</v>
       </c>
-      <c r="F9" s="3" t="n">
-        <v>3897000000</v>
-      </c>
       <c r="G9" s="3" t="n"/>
+      <c r="H9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -5990,21 +8210,22 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
+        <v>40000000</v>
+      </c>
+      <c r="C10" s="3" t="n">
         <v>731000000</v>
       </c>
-      <c r="C10" s="3" t="n">
+      <c r="D10" s="3" t="n">
         <v>372000000</v>
       </c>
-      <c r="D10" s="3" t="n">
+      <c r="E10" s="3" t="n">
         <v>-1606000000</v>
       </c>
-      <c r="E10" s="3" t="n">
+      <c r="F10" s="3" t="n">
         <v>2248000000</v>
       </c>
-      <c r="F10" s="3" t="n">
-        <v>-86000000</v>
-      </c>
       <c r="G10" s="3" t="n"/>
+      <c r="H10" s="3" t="n"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -6013,21 +8234,22 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
+        <v>-350000000</v>
+      </c>
+      <c r="C11" s="3" t="n">
         <v>-328000000</v>
       </c>
-      <c r="C11" s="3" t="n">
+      <c r="D11" s="3" t="n">
         <v>-450000000</v>
       </c>
-      <c r="D11" s="3" t="n">
+      <c r="E11" s="3" t="n">
         <v>-1319000000</v>
       </c>
-      <c r="E11" s="3" t="n">
+      <c r="F11" s="3" t="n">
         <v>1666000000</v>
       </c>
-      <c r="F11" s="3" t="n">
-        <v>-171000000</v>
-      </c>
       <c r="G11" s="3" t="n"/>
+      <c r="H11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -6036,21 +8258,22 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
+        <v>-350000000</v>
+      </c>
+      <c r="C12" s="3" t="n">
         <v>-328000000</v>
       </c>
-      <c r="C12" s="3" t="n">
+      <c r="D12" s="3" t="n">
         <v>-450000000</v>
       </c>
-      <c r="D12" s="3" t="n">
+      <c r="E12" s="3" t="n">
         <v>-1319000000</v>
       </c>
-      <c r="E12" s="3" t="n">
+      <c r="F12" s="3" t="n">
         <v>1666000000</v>
       </c>
-      <c r="F12" s="3" t="n">
-        <v>-171000000</v>
-      </c>
       <c r="G12" s="3" t="n"/>
+      <c r="H12" s="3" t="n"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -6062,12 +8285,13 @@
       <c r="C13" s="3" t="n"/>
       <c r="D13" s="3" t="n"/>
       <c r="E13" s="3" t="n"/>
-      <c r="F13" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="F13" s="3" t="n"/>
       <c r="G13" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="H13" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -6076,21 +8300,22 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="C14" s="3" t="n">
         <v>116000000</v>
       </c>
-      <c r="C14" s="3" t="n">
+      <c r="D14" s="3" t="n">
         <v>10000000</v>
       </c>
-      <c r="D14" s="3" t="n">
+      <c r="E14" s="3" t="n">
         <v>155000000</v>
       </c>
-      <c r="E14" s="3" t="n">
+      <c r="F14" s="3" t="n">
         <v>4000000</v>
       </c>
-      <c r="F14" s="3" t="n">
-        <v>127000000</v>
-      </c>
       <c r="G14" s="3" t="n"/>
+      <c r="H14" s="3" t="n"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -6099,21 +8324,22 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
+        <v>-355000000</v>
+      </c>
+      <c r="C15" s="3" t="n">
         <v>-160000000</v>
       </c>
-      <c r="C15" s="3" t="n">
+      <c r="D15" s="3" t="n">
         <v>-460000000</v>
       </c>
-      <c r="D15" s="3" t="n">
+      <c r="E15" s="3" t="n">
         <v>-524000000</v>
       </c>
-      <c r="E15" s="3" t="n">
+      <c r="F15" s="3" t="n">
         <v>-779000000</v>
       </c>
-      <c r="F15" s="3" t="n">
-        <v>-298000000</v>
-      </c>
       <c r="G15" s="3" t="n"/>
+      <c r="H15" s="3" t="n"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -6122,21 +8348,22 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
+        <v>-355000000</v>
+      </c>
+      <c r="C16" s="3" t="n">
         <v>-160000000</v>
       </c>
-      <c r="C16" s="3" t="n">
+      <c r="D16" s="3" t="n">
         <v>-460000000</v>
       </c>
-      <c r="D16" s="3" t="n">
+      <c r="E16" s="3" t="n">
         <v>-524000000</v>
       </c>
-      <c r="E16" s="3" t="n">
+      <c r="F16" s="3" t="n">
         <v>-779000000</v>
       </c>
-      <c r="F16" s="3" t="n">
-        <v>-298000000</v>
-      </c>
       <c r="G16" s="3" t="n"/>
+      <c r="H16" s="3" t="n"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -6151,15 +8378,16 @@
         <v>0</v>
       </c>
       <c r="D17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="3" t="n">
         <v>-950000000</v>
       </c>
-      <c r="E17" s="3" t="n">
+      <c r="F17" s="3" t="n">
         <v>2441000000</v>
       </c>
-      <c r="F17" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="G17" s="3" t="n"/>
+      <c r="H17" s="3" t="n"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -6170,11 +8398,12 @@
       <c r="B18" s="3" t="n"/>
       <c r="C18" s="3" t="n"/>
       <c r="D18" s="3" t="n"/>
-      <c r="E18" s="3" t="n">
+      <c r="E18" s="3" t="n"/>
+      <c r="F18" s="3" t="n">
         <v>947000000</v>
       </c>
-      <c r="F18" s="3" t="n"/>
       <c r="G18" s="3" t="n"/>
+      <c r="H18" s="3" t="n"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -6185,11 +8414,12 @@
       <c r="B19" s="3" t="n"/>
       <c r="C19" s="3" t="n"/>
       <c r="D19" s="3" t="n"/>
-      <c r="E19" s="3" t="n">
+      <c r="E19" s="3" t="n"/>
+      <c r="F19" s="3" t="n">
         <v>947000000</v>
       </c>
-      <c r="F19" s="3" t="n"/>
       <c r="G19" s="3" t="n"/>
+      <c r="H19" s="3" t="n"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -6204,15 +8434,16 @@
         <v>0</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>-3000000</v>
+        <v>0</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>1494000000</v>
+        <v>-950000000</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>0</v>
+        <v>2441000000</v>
       </c>
       <c r="G20" s="3" t="n"/>
+      <c r="H20" s="3" t="n"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -6220,20 +8451,21 @@
           <t>Long Term Debt Payments</t>
         </is>
       </c>
-      <c r="B21" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="B21" s="3" t="n"/>
       <c r="C21" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D21" s="3" t="n"/>
+      <c r="D21" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="3" t="n"/>
-      <c r="F21" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="F21" s="3" t="n"/>
       <c r="G21" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="H21" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -6248,13 +8480,16 @@
         <v>0</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>947000000</v>
+        <v>0</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>1494000000</v>
-      </c>
-      <c r="F22" s="3" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>2441000000</v>
+      </c>
       <c r="G22" s="3" t="n"/>
+      <c r="H22" s="3" t="n"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -6263,21 +8498,22 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
+        <v>-2565000000</v>
+      </c>
+      <c r="C23" s="3" t="n">
         <v>-1541000000</v>
       </c>
-      <c r="C23" s="3" t="n">
+      <c r="D23" s="3" t="n">
         <v>-1337000000</v>
       </c>
-      <c r="D23" s="3" t="n">
+      <c r="E23" s="3" t="n">
         <v>-2298000000</v>
       </c>
-      <c r="E23" s="3" t="n">
+      <c r="F23" s="3" t="n">
         <v>-357000000</v>
       </c>
-      <c r="F23" s="3" t="n">
-        <v>-1214000000</v>
-      </c>
       <c r="G23" s="3" t="n"/>
+      <c r="H23" s="3" t="n"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -6285,16 +8521,17 @@
           <t>Cash From Discontinued Investing Activities</t>
         </is>
       </c>
-      <c r="B24" s="3" t="n">
+      <c r="B24" s="3" t="n"/>
+      <c r="C24" s="3" t="n">
         <v>1348000000</v>
       </c>
-      <c r="C24" s="3" t="n">
+      <c r="D24" s="3" t="n">
         <v>-8000000</v>
       </c>
-      <c r="D24" s="3" t="n"/>
       <c r="E24" s="3" t="n"/>
       <c r="F24" s="3" t="n"/>
       <c r="G24" s="3" t="n"/>
+      <c r="H24" s="3" t="n"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -6303,21 +8540,22 @@
         </is>
       </c>
       <c r="B25" s="3" t="n">
+        <v>-2565000000</v>
+      </c>
+      <c r="C25" s="3" t="n">
         <v>-2889000000</v>
       </c>
-      <c r="C25" s="3" t="n">
+      <c r="D25" s="3" t="n">
         <v>-1329000000</v>
       </c>
-      <c r="D25" s="3" t="n">
+      <c r="E25" s="3" t="n">
         <v>-2276000000</v>
       </c>
-      <c r="E25" s="3" t="n">
+      <c r="F25" s="3" t="n">
         <v>-357000000</v>
       </c>
-      <c r="F25" s="3" t="n">
-        <v>-1214000000</v>
-      </c>
       <c r="G25" s="3" t="n"/>
+      <c r="H25" s="3" t="n"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -6329,10 +8567,11 @@
       <c r="C26" s="3" t="n"/>
       <c r="D26" s="3" t="n"/>
       <c r="E26" s="3" t="n"/>
-      <c r="F26" s="3" t="n">
+      <c r="F26" s="3" t="n"/>
+      <c r="G26" s="3" t="n">
         <v>31000000</v>
       </c>
-      <c r="G26" s="3" t="n">
+      <c r="H26" s="3" t="n">
         <v>-17000000</v>
       </c>
     </row>
@@ -6343,21 +8582,22 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
+        <v>-2176000000</v>
+      </c>
+      <c r="C27" s="3" t="n">
         <v>-2633000000</v>
       </c>
-      <c r="C27" s="3" t="n">
+      <c r="D27" s="3" t="n">
         <v>-1071000000</v>
       </c>
-      <c r="D27" s="3" t="n">
+      <c r="E27" s="3" t="n">
         <v>-278000000</v>
       </c>
-      <c r="E27" s="3" t="n">
+      <c r="F27" s="3" t="n">
         <v>-145000000</v>
       </c>
-      <c r="F27" s="3" t="n">
-        <v>-1037000000</v>
-      </c>
       <c r="G27" s="3" t="n"/>
+      <c r="H27" s="3" t="n"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -6366,21 +8606,22 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
+        <v>778000000</v>
+      </c>
+      <c r="C28" s="3" t="n">
         <v>797000000</v>
       </c>
-      <c r="C28" s="3" t="n">
+      <c r="D28" s="3" t="n">
         <v>317000000</v>
       </c>
-      <c r="D28" s="3" t="n">
+      <c r="E28" s="3" t="n">
         <v>333000000</v>
       </c>
-      <c r="E28" s="3" t="n">
+      <c r="F28" s="3" t="n">
         <v>398000000</v>
       </c>
-      <c r="F28" s="3" t="n">
-        <v>90000000</v>
-      </c>
       <c r="G28" s="3" t="n"/>
+      <c r="H28" s="3" t="n"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -6389,21 +8630,22 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
+        <v>-2954000000</v>
+      </c>
+      <c r="C29" s="3" t="n">
         <v>-3430000000</v>
       </c>
-      <c r="C29" s="3" t="n">
+      <c r="D29" s="3" t="n">
         <v>-1388000000</v>
       </c>
-      <c r="D29" s="3" t="n">
+      <c r="E29" s="3" t="n">
         <v>-611000000</v>
       </c>
-      <c r="E29" s="3" t="n">
+      <c r="F29" s="3" t="n">
         <v>-543000000</v>
       </c>
-      <c r="F29" s="3" t="n">
-        <v>-1127000000</v>
-      </c>
       <c r="G29" s="3" t="n"/>
+      <c r="H29" s="3" t="n"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -6411,18 +8653,19 @@
           <t>Net Business Purchase And Sale</t>
         </is>
       </c>
-      <c r="B30" s="3" t="n">
+      <c r="B30" s="3" t="n"/>
+      <c r="C30" s="3" t="n">
         <v>-44000000</v>
       </c>
-      <c r="C30" s="3" t="n">
+      <c r="D30" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D30" s="3" t="n"/>
       <c r="E30" s="3" t="n"/>
-      <c r="F30" s="3" t="n">
+      <c r="F30" s="3" t="n"/>
+      <c r="G30" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G30" s="3" t="n">
+      <c r="H30" s="3" t="n">
         <v>-565000000</v>
       </c>
     </row>
@@ -6432,18 +8675,19 @@
           <t>Purchase Of Business</t>
         </is>
       </c>
-      <c r="B31" s="3" t="n">
+      <c r="B31" s="3" t="n"/>
+      <c r="C31" s="3" t="n">
         <v>-44000000</v>
       </c>
-      <c r="C31" s="3" t="n">
+      <c r="D31" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D31" s="3" t="n"/>
       <c r="E31" s="3" t="n"/>
-      <c r="F31" s="3" t="n">
+      <c r="F31" s="3" t="n"/>
+      <c r="G31" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G31" s="3" t="n">
+      <c r="H31" s="3" t="n">
         <v>-565000000</v>
       </c>
     </row>
@@ -6454,21 +8698,22 @@
         </is>
       </c>
       <c r="B32" s="3" t="n">
+        <v>-389000000</v>
+      </c>
+      <c r="C32" s="3" t="n">
         <v>-222000000</v>
       </c>
-      <c r="C32" s="3" t="n">
+      <c r="D32" s="3" t="n">
         <v>-258000000</v>
       </c>
-      <c r="D32" s="3" t="n">
+      <c r="E32" s="3" t="n">
         <v>-282000000</v>
       </c>
-      <c r="E32" s="3" t="n">
+      <c r="F32" s="3" t="n">
         <v>-212000000</v>
       </c>
-      <c r="F32" s="3" t="n">
-        <v>-208000000</v>
-      </c>
       <c r="G32" s="3" t="n"/>
+      <c r="H32" s="3" t="n"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -6477,21 +8722,22 @@
         </is>
       </c>
       <c r="B33" s="3" t="n">
+        <v>-389000000</v>
+      </c>
+      <c r="C33" s="3" t="n">
         <v>-222000000</v>
       </c>
-      <c r="C33" s="3" t="n">
+      <c r="D33" s="3" t="n">
         <v>-258000000</v>
       </c>
-      <c r="D33" s="3" t="n">
+      <c r="E33" s="3" t="n">
         <v>-282000000</v>
       </c>
-      <c r="E33" s="3" t="n">
+      <c r="F33" s="3" t="n">
         <v>-212000000</v>
       </c>
-      <c r="F33" s="3" t="n">
-        <v>-208000000</v>
-      </c>
       <c r="G33" s="3" t="n"/>
+      <c r="H33" s="3" t="n"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -6500,21 +8746,22 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
+        <v>2955000000</v>
+      </c>
+      <c r="C34" s="3" t="n">
         <v>2600000000</v>
       </c>
-      <c r="C34" s="3" t="n">
+      <c r="D34" s="3" t="n">
         <v>2159000000</v>
       </c>
-      <c r="D34" s="3" t="n">
+      <c r="E34" s="3" t="n">
         <v>2011000000</v>
       </c>
-      <c r="E34" s="3" t="n">
+      <c r="F34" s="3" t="n">
         <v>939000000</v>
       </c>
-      <c r="F34" s="3" t="n">
-        <v>1299000000</v>
-      </c>
       <c r="G34" s="3" t="n"/>
+      <c r="H34" s="3" t="n"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -6522,16 +8769,17 @@
           <t>Cash From Discontinued Operating Activities</t>
         </is>
       </c>
-      <c r="B35" s="3" t="n">
+      <c r="B35" s="3" t="n"/>
+      <c r="C35" s="3" t="n">
         <v>296000000</v>
       </c>
-      <c r="C35" s="3" t="n">
+      <c r="D35" s="3" t="n">
         <v>371000000</v>
       </c>
-      <c r="D35" s="3" t="n"/>
       <c r="E35" s="3" t="n"/>
       <c r="F35" s="3" t="n"/>
       <c r="G35" s="3" t="n"/>
+      <c r="H35" s="3" t="n"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -6540,21 +8788,22 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
+        <v>2955000000</v>
+      </c>
+      <c r="C36" s="3" t="n">
         <v>2304000000</v>
       </c>
-      <c r="C36" s="3" t="n">
+      <c r="D36" s="3" t="n">
         <v>1788000000</v>
       </c>
-      <c r="D36" s="3" t="n">
+      <c r="E36" s="3" t="n">
         <v>1462000000</v>
       </c>
-      <c r="E36" s="3" t="n">
+      <c r="F36" s="3" t="n">
         <v>939000000</v>
       </c>
-      <c r="F36" s="3" t="n">
-        <v>1299000000</v>
-      </c>
       <c r="G36" s="3" t="n"/>
+      <c r="H36" s="3" t="n"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -6563,21 +8812,22 @@
         </is>
       </c>
       <c r="B37" s="3" t="n">
+        <v>456000000</v>
+      </c>
+      <c r="C37" s="3" t="n">
         <v>-1386000000</v>
       </c>
-      <c r="C37" s="3" t="n">
+      <c r="D37" s="3" t="n">
         <v>-708000000</v>
       </c>
-      <c r="D37" s="3" t="n">
+      <c r="E37" s="3" t="n">
         <v>464000000</v>
       </c>
-      <c r="E37" s="3" t="n">
+      <c r="F37" s="3" t="n">
         <v>-748000000</v>
       </c>
-      <c r="F37" s="3" t="n">
-        <v>-70000000</v>
-      </c>
       <c r="G37" s="3" t="n"/>
+      <c r="H37" s="3" t="n"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -6589,10 +8839,11 @@
       <c r="C38" s="3" t="n"/>
       <c r="D38" s="3" t="n"/>
       <c r="E38" s="3" t="n"/>
-      <c r="F38" s="3" t="n">
+      <c r="F38" s="3" t="n"/>
+      <c r="G38" s="3" t="n">
         <v>30000000</v>
       </c>
-      <c r="G38" s="3" t="n">
+      <c r="H38" s="3" t="n">
         <v>36000000</v>
       </c>
     </row>
@@ -6603,21 +8854,22 @@
         </is>
       </c>
       <c r="B39" s="3" t="n">
+        <v>609000000</v>
+      </c>
+      <c r="C39" s="3" t="n">
         <v>-910000000</v>
       </c>
-      <c r="C39" s="3" t="n">
+      <c r="D39" s="3" t="n">
         <v>895000000</v>
       </c>
-      <c r="D39" s="3" t="n">
+      <c r="E39" s="3" t="n">
         <v>535000000</v>
       </c>
-      <c r="E39" s="3" t="n">
+      <c r="F39" s="3" t="n">
         <v>-577000000</v>
       </c>
-      <c r="F39" s="3" t="n">
-        <v>-328000000</v>
-      </c>
       <c r="G39" s="3" t="n"/>
+      <c r="H39" s="3" t="n"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -6626,21 +8878,22 @@
         </is>
       </c>
       <c r="B40" s="3" t="n">
+        <v>713000000</v>
+      </c>
+      <c r="C40" s="3" t="n">
         <v>-322000000</v>
       </c>
-      <c r="C40" s="3" t="n">
+      <c r="D40" s="3" t="n">
         <v>444000000</v>
       </c>
-      <c r="D40" s="3" t="n">
+      <c r="E40" s="3" t="n">
         <v>-301000000</v>
       </c>
-      <c r="E40" s="3" t="n">
+      <c r="F40" s="3" t="n">
         <v>-288000000</v>
       </c>
-      <c r="F40" s="3" t="n">
-        <v>257000000</v>
-      </c>
       <c r="G40" s="3" t="n"/>
+      <c r="H40" s="3" t="n"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -6649,21 +8902,22 @@
         </is>
       </c>
       <c r="B41" s="3" t="n">
+        <v>-104000000</v>
+      </c>
+      <c r="C41" s="3" t="n">
         <v>-588000000</v>
       </c>
-      <c r="C41" s="3" t="n">
+      <c r="D41" s="3" t="n">
         <v>451000000</v>
       </c>
-      <c r="D41" s="3" t="n">
+      <c r="E41" s="3" t="n">
         <v>836000000</v>
       </c>
-      <c r="E41" s="3" t="n">
+      <c r="F41" s="3" t="n">
         <v>-289000000</v>
       </c>
-      <c r="F41" s="3" t="n">
-        <v>-585000000</v>
-      </c>
       <c r="G41" s="3" t="n"/>
+      <c r="H41" s="3" t="n"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -6672,21 +8926,22 @@
         </is>
       </c>
       <c r="B42" s="3" t="n">
+        <v>-104000000</v>
+      </c>
+      <c r="C42" s="3" t="n">
         <v>-588000000</v>
       </c>
-      <c r="C42" s="3" t="n">
+      <c r="D42" s="3" t="n">
         <v>451000000</v>
       </c>
-      <c r="D42" s="3" t="n">
+      <c r="E42" s="3" t="n">
         <v>836000000</v>
       </c>
-      <c r="E42" s="3" t="n">
+      <c r="F42" s="3" t="n">
         <v>-289000000</v>
       </c>
-      <c r="F42" s="3" t="n">
-        <v>-585000000</v>
-      </c>
       <c r="G42" s="3" t="n"/>
+      <c r="H42" s="3" t="n"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -6695,21 +8950,22 @@
         </is>
       </c>
       <c r="B43" s="3" t="n">
+        <v>-308000000</v>
+      </c>
+      <c r="C43" s="3" t="n">
         <v>248000000</v>
       </c>
-      <c r="C43" s="3" t="n">
+      <c r="D43" s="3" t="n">
         <v>118000000</v>
       </c>
-      <c r="D43" s="3" t="n">
+      <c r="E43" s="3" t="n">
         <v>-140000000</v>
       </c>
-      <c r="E43" s="3" t="n">
+      <c r="F43" s="3" t="n">
         <v>-237000000</v>
       </c>
-      <c r="F43" s="3" t="n">
-        <v>593000000</v>
-      </c>
       <c r="G43" s="3" t="n"/>
+      <c r="H43" s="3" t="n"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -6718,21 +8974,22 @@
         </is>
       </c>
       <c r="B44" s="3" t="n">
+        <v>-125000000</v>
+      </c>
+      <c r="C44" s="3" t="n">
         <v>-610000000</v>
       </c>
-      <c r="C44" s="3" t="n">
+      <c r="D44" s="3" t="n">
         <v>-636000000</v>
       </c>
-      <c r="D44" s="3" t="n">
+      <c r="E44" s="3" t="n">
         <v>-261000000</v>
       </c>
-      <c r="E44" s="3" t="n">
+      <c r="F44" s="3" t="n">
         <v>-682000000</v>
       </c>
-      <c r="F44" s="3" t="n">
-        <v>-362000000</v>
-      </c>
       <c r="G44" s="3" t="n"/>
+      <c r="H44" s="3" t="n"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -6741,21 +8998,22 @@
         </is>
       </c>
       <c r="B45" s="3" t="n">
+        <v>280000000</v>
+      </c>
+      <c r="C45" s="3" t="n">
         <v>-114000000</v>
       </c>
-      <c r="C45" s="3" t="n">
+      <c r="D45" s="3" t="n">
         <v>-1085000000</v>
       </c>
-      <c r="D45" s="3" t="n">
+      <c r="E45" s="3" t="n">
         <v>330000000</v>
       </c>
-      <c r="E45" s="3" t="n">
+      <c r="F45" s="3" t="n">
         <v>748000000</v>
       </c>
-      <c r="F45" s="3" t="n">
-        <v>-3000000</v>
-      </c>
       <c r="G45" s="3" t="n"/>
+      <c r="H45" s="3" t="n"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -6764,21 +9022,22 @@
         </is>
       </c>
       <c r="B46" s="3" t="n">
+        <v>280000000</v>
+      </c>
+      <c r="C46" s="3" t="n">
         <v>-114000000</v>
       </c>
-      <c r="C46" s="3" t="n">
+      <c r="D46" s="3" t="n">
         <v>-1085000000</v>
       </c>
-      <c r="D46" s="3" t="n">
+      <c r="E46" s="3" t="n">
         <v>330000000</v>
       </c>
-      <c r="E46" s="3" t="n">
+      <c r="F46" s="3" t="n">
         <v>748000000</v>
       </c>
-      <c r="F46" s="3" t="n">
-        <v>-3000000</v>
-      </c>
       <c r="G46" s="3" t="n"/>
+      <c r="H46" s="3" t="n"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -6787,21 +9046,22 @@
         </is>
       </c>
       <c r="B47" s="3" t="n">
+        <v>28000000</v>
+      </c>
+      <c r="C47" s="3" t="n">
         <v>91000000</v>
       </c>
-      <c r="C47" s="3" t="n">
+      <c r="D47" s="3" t="n">
         <v>-67000000</v>
       </c>
-      <c r="D47" s="3" t="n">
-        <v>-10000000</v>
-      </c>
       <c r="E47" s="3" t="n">
-        <v>39000000</v>
+        <v>-8000000</v>
       </c>
       <c r="F47" s="3" t="n">
-        <v>62000000</v>
+        <v>37000000</v>
       </c>
       <c r="G47" s="3" t="n"/>
+      <c r="H47" s="3" t="n"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -6810,21 +9070,22 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
+        <v>487000000</v>
+      </c>
+      <c r="C48" s="3" t="n">
         <v>486000000</v>
       </c>
-      <c r="C48" s="3" t="n">
+      <c r="D48" s="3" t="n">
         <v>419000000</v>
       </c>
-      <c r="D48" s="3" t="n">
+      <c r="E48" s="3" t="n">
         <v>369000000</v>
       </c>
-      <c r="E48" s="3" t="n">
+      <c r="F48" s="3" t="n">
         <v>364000000</v>
       </c>
-      <c r="F48" s="3" t="n">
-        <v>339000000</v>
-      </c>
       <c r="G48" s="3" t="n"/>
+      <c r="H48" s="3" t="n"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -6833,21 +9094,22 @@
         </is>
       </c>
       <c r="B49" s="3" t="n">
+        <v>-79000000</v>
+      </c>
+      <c r="C49" s="3" t="n">
         <v>1083000000</v>
       </c>
-      <c r="C49" s="3" t="n">
+      <c r="D49" s="3" t="n">
         <v>218000000</v>
       </c>
-      <c r="D49" s="3" t="n">
+      <c r="E49" s="3" t="n">
         <v>-886000000</v>
       </c>
-      <c r="E49" s="3" t="n">
+      <c r="F49" s="3" t="n">
         <v>-167000000</v>
       </c>
-      <c r="F49" s="3" t="n">
-        <v>-300000000</v>
-      </c>
       <c r="G49" s="3" t="n"/>
+      <c r="H49" s="3" t="n"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -6856,21 +9118,22 @@
         </is>
       </c>
       <c r="B50" s="3" t="n">
+        <v>-79000000</v>
+      </c>
+      <c r="C50" s="3" t="n">
         <v>1083000000</v>
       </c>
-      <c r="C50" s="3" t="n">
+      <c r="D50" s="3" t="n">
         <v>218000000</v>
       </c>
-      <c r="D50" s="3" t="n">
+      <c r="E50" s="3" t="n">
         <v>-886000000</v>
       </c>
-      <c r="E50" s="3" t="n">
+      <c r="F50" s="3" t="n">
         <v>-167000000</v>
       </c>
-      <c r="F50" s="3" t="n">
-        <v>-300000000</v>
-      </c>
       <c r="G50" s="3" t="n"/>
+      <c r="H50" s="3" t="n"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -6879,21 +9142,22 @@
         </is>
       </c>
       <c r="B51" s="3" t="n">
+        <v>757000000</v>
+      </c>
+      <c r="C51" s="3" t="n">
         <v>751000000</v>
       </c>
-      <c r="C51" s="3" t="n">
+      <c r="D51" s="3" t="n">
         <v>754000000</v>
       </c>
-      <c r="D51" s="3" t="n">
+      <c r="E51" s="3" t="n">
         <v>757000000</v>
       </c>
-      <c r="E51" s="3" t="n">
+      <c r="F51" s="3" t="n">
         <v>742000000</v>
       </c>
-      <c r="F51" s="3" t="n">
-        <v>786000000</v>
-      </c>
       <c r="G51" s="3" t="n"/>
+      <c r="H51" s="3" t="n"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -6902,21 +9166,22 @@
         </is>
       </c>
       <c r="B52" s="3" t="n">
+        <v>757000000</v>
+      </c>
+      <c r="C52" s="3" t="n">
         <v>751000000</v>
       </c>
-      <c r="C52" s="3" t="n">
+      <c r="D52" s="3" t="n">
         <v>754000000</v>
       </c>
-      <c r="D52" s="3" t="n">
+      <c r="E52" s="3" t="n">
         <v>757000000</v>
       </c>
-      <c r="E52" s="3" t="n">
+      <c r="F52" s="3" t="n">
         <v>742000000</v>
       </c>
-      <c r="F52" s="3" t="n">
-        <v>786000000</v>
-      </c>
       <c r="G52" s="3" t="n"/>
+      <c r="H52" s="3" t="n"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -6925,19 +9190,22 @@
         </is>
       </c>
       <c r="B53" s="3" t="n">
+        <v>551000000</v>
+      </c>
+      <c r="C53" s="3" t="n">
         <v>557000000</v>
       </c>
-      <c r="C53" s="3" t="n">
+      <c r="D53" s="3" t="n">
         <v>562000000</v>
       </c>
-      <c r="D53" s="3" t="n">
+      <c r="E53" s="3" t="n">
         <v>568000000</v>
       </c>
-      <c r="E53" s="3" t="n">
+      <c r="F53" s="3" t="n">
         <v>567000000</v>
       </c>
-      <c r="F53" s="3" t="n"/>
       <c r="G53" s="3" t="n"/>
+      <c r="H53" s="3" t="n"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -6946,19 +9214,22 @@
         </is>
       </c>
       <c r="B54" s="3" t="n">
+        <v>551000000</v>
+      </c>
+      <c r="C54" s="3" t="n">
         <v>557000000</v>
       </c>
-      <c r="C54" s="3" t="n">
+      <c r="D54" s="3" t="n">
         <v>562000000</v>
       </c>
-      <c r="D54" s="3" t="n">
+      <c r="E54" s="3" t="n">
         <v>568000000</v>
       </c>
-      <c r="E54" s="3" t="n">
+      <c r="F54" s="3" t="n">
         <v>567000000</v>
       </c>
-      <c r="F54" s="3" t="n"/>
       <c r="G54" s="3" t="n"/>
+      <c r="H54" s="3" t="n"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -6967,51 +9238,89 @@
         </is>
       </c>
       <c r="B55" s="3" t="n">
+        <v>206000000</v>
+      </c>
+      <c r="C55" s="3" t="n">
         <v>194000000</v>
       </c>
-      <c r="C55" s="3" t="n">
+      <c r="D55" s="3" t="n">
         <v>192000000</v>
       </c>
-      <c r="D55" s="3" t="n">
+      <c r="E55" s="3" t="n">
         <v>189000000</v>
       </c>
-      <c r="E55" s="3" t="n">
+      <c r="F55" s="3" t="n">
         <v>175000000</v>
       </c>
-      <c r="F55" s="3" t="n">
-        <v>-1607000000</v>
-      </c>
       <c r="G55" s="3" t="n"/>
+      <c r="H55" s="3" t="n"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
+          <t>Operating Gains Losses</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="n">
+        <v>-66000000</v>
+      </c>
+      <c r="C56" s="3" t="n"/>
+      <c r="D56" s="3" t="n"/>
+      <c r="E56" s="3" t="n"/>
+      <c r="F56" s="3" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="G56" s="3" t="n"/>
+      <c r="H56" s="3" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Gain Loss On Investment Securities</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="n">
+        <v>-66000000</v>
+      </c>
+      <c r="C57" s="3" t="n"/>
+      <c r="D57" s="3" t="n"/>
+      <c r="E57" s="3" t="n"/>
+      <c r="F57" s="3" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="G57" s="3" t="n"/>
+      <c r="H57" s="3" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
           <t>Net Income From Continuing Operations</t>
         </is>
       </c>
-      <c r="B56" s="3" t="n">
+      <c r="B58" s="3" t="n">
+        <v>1372000000</v>
+      </c>
+      <c r="C58" s="3" t="n">
         <v>1620000000</v>
       </c>
-      <c r="C56" s="3" t="n">
+      <c r="D58" s="3" t="n">
         <v>1172000000</v>
       </c>
-      <c r="D56" s="3" t="n">
+      <c r="E58" s="3" t="n">
         <v>768000000</v>
       </c>
-      <c r="E56" s="3" t="n">
+      <c r="F58" s="3" t="n">
         <v>709000000</v>
       </c>
-      <c r="F56" s="3" t="n">
-        <v>482000000</v>
-      </c>
-      <c r="G56" s="3" t="n"/>
+      <c r="G58" s="3" t="n"/>
+      <c r="H58" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7039,12 +9348,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>FY Summary</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>no gaps detected</t>
+          <t>'Net Debt' not found in statements — left blank</t>
         </is>
       </c>
     </row>
